--- a/AAII_Financials/Quarterly/FABP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FABP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
   <si>
     <t>FABP</t>
   </si>
@@ -656,91 +656,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>8800</v>
+      </c>
+      <c r="I8" s="3">
         <v>7600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>7600</v>
       </c>
-      <c r="I8" s="3">
-        <v>8900</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -768,37 +773,43 @@
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E10" s="3">
         <v>8800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>8800</v>
+      </c>
+      <c r="I10" s="3">
         <v>7600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>7600</v>
       </c>
-      <c r="I10" s="3">
-        <v>8900</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,8 +821,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -839,8 +851,11 @@
       <c r="K12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,8 +883,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -897,8 +915,11 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -926,8 +947,11 @@
       <c r="K15" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -936,66 +960,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E17" s="3">
         <v>6300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I17" s="3">
         <v>5900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5400</v>
       </c>
-      <c r="I17" s="3">
-        <v>5400</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E18" s="3">
         <v>2500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I18" s="3">
         <v>1700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2100</v>
       </c>
-      <c r="I18" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1007,8 +1038,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1031,42 +1063,48 @@
         <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E21" s="3">
         <v>2600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I21" s="3">
         <v>1700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>2200</v>
       </c>
-      <c r="I21" s="3">
-        <v>3600</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1094,66 +1132,75 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E23" s="3">
         <v>2400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I23" s="3">
         <v>1600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2000</v>
       </c>
-      <c r="I23" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
-      </c>
-      <c r="G24" s="3">
-        <v>100</v>
       </c>
       <c r="H24" s="3">
         <v>300</v>
       </c>
       <c r="I24" s="3">
+        <v>100</v>
+      </c>
+      <c r="J24" s="3">
+        <v>300</v>
+      </c>
+      <c r="K24" s="3">
+        <v>500</v>
+      </c>
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
-        <v>500</v>
-      </c>
-      <c r="K24" s="3">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1181,66 +1228,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E26" s="3">
         <v>2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I26" s="3">
         <v>1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>2800</v>
       </c>
-      <c r="J26" s="3">
-        <v>2800</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E27" s="3">
         <v>2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I27" s="3">
         <v>1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>2800</v>
       </c>
-      <c r="J27" s="3">
-        <v>2800</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1268,8 +1324,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1297,8 +1356,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1326,8 +1388,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1355,8 +1420,11 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1379,42 +1447,48 @@
         <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E33" s="3">
         <v>2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I33" s="3">
         <v>1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>2800</v>
       </c>
-      <c r="J33" s="3">
-        <v>2800</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1442,71 +1516,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E35" s="3">
         <v>2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I35" s="3">
         <v>1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>2800</v>
       </c>
-      <c r="J35" s="3">
-        <v>2800</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1518,8 +1601,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1531,37 +1615,41 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E41" s="3">
         <v>22000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>46600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>51200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I41" s="3">
         <v>68900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>35200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>18600</v>
       </c>
-      <c r="J41" s="3">
-        <v>18600</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1569,28 +1657,31 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>800</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>1300</v>
       </c>
-      <c r="I42" s="3">
-        <v>500</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>700</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1618,8 +1709,11 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1647,124 +1741,139 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E45" s="3">
         <v>18000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>21300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>19000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>25200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>22800</v>
       </c>
-      <c r="I45" s="3">
-        <v>21800</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22200</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E46" s="3">
         <v>41200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>69500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>70900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I46" s="3">
         <v>96600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>59800</v>
       </c>
-      <c r="I46" s="3">
-        <v>41600</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>41800</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>187000</v>
+      </c>
+      <c r="E47" s="3">
         <v>192800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>177400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>186100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3">
         <v>173300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>181400</v>
       </c>
-      <c r="I47" s="3">
-        <v>187100</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>188300</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E48" s="3">
         <v>17300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3">
         <v>10900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>8500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>8100</v>
       </c>
-      <c r="J48" s="3">
-        <v>8100</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1792,8 +1901,11 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1821,8 +1933,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1850,37 +1965,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E52" s="3">
         <v>23800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>23700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>23600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3">
         <v>23400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>23300</v>
       </c>
-      <c r="I52" s="3">
-        <v>23300</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>23200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1908,37 +2029,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1038300</v>
+      </c>
+      <c r="E54" s="3">
         <v>995700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>987700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>992200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I54" s="3">
         <v>948800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>898500</v>
       </c>
-      <c r="I54" s="3">
-        <v>852100</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>851700</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1950,8 +2077,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1963,66 +2091,73 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>743200</v>
+      </c>
+      <c r="E57" s="3">
         <v>774900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>759000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>731200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3">
         <v>700300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>664900</v>
       </c>
-      <c r="I57" s="3">
-        <v>671300</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>640800</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E58" s="3">
         <v>44900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>94100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>69000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>67700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>66300</v>
       </c>
-      <c r="I58" s="3">
-        <v>27900</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>31800</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2050,71 +2185,80 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>795000</v>
+      </c>
+      <c r="E60" s="3">
         <v>828500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>865200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>811100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="3">
         <v>777000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>741200</v>
       </c>
-      <c r="I60" s="3">
-        <v>706100</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>679100</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>172300</v>
+      </c>
+      <c r="E61" s="3">
         <v>92400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>54700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>112000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>112100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>91100</v>
       </c>
-      <c r="I61" s="3">
-        <v>78700</v>
-      </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>109700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>5</v>
+      <c r="D62" s="3">
+        <v>0</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>5</v>
@@ -2137,8 +2281,11 @@
       <c r="K62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2166,8 +2313,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2195,8 +2345,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2224,37 +2377,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>967300</v>
+      </c>
+      <c r="E66" s="3">
         <v>920900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>919900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>923100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I66" s="3">
         <v>889200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>832400</v>
       </c>
-      <c r="I66" s="3">
-        <v>784800</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>788800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2266,8 +2425,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2295,8 +2455,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2324,8 +2487,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2353,8 +2519,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2382,37 +2551,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>90700</v>
+      </c>
+      <c r="E72" s="3">
         <v>88600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>87200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>88800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I72" s="3">
         <v>85900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>86700</v>
       </c>
-      <c r="I72" s="3">
-        <v>85700</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>83400</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2440,8 +2615,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2469,8 +2647,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2498,37 +2679,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E76" s="3">
         <v>74800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>67800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>69100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I76" s="3">
         <v>59700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>66100</v>
       </c>
-      <c r="I76" s="3">
-        <v>67300</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>62900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>60700</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2556,71 +2743,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E81" s="3">
         <v>2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I81" s="3">
         <v>1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>2800</v>
       </c>
-      <c r="J81" s="3">
-        <v>2800</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2632,8 +2828,9 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2661,8 +2858,11 @@
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2690,8 +2890,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2719,8 +2922,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2748,8 +2954,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2777,8 +2986,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2806,8 +3018,11 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -2835,8 +3050,11 @@
       <c r="K89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2848,8 +3066,9 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2877,8 +3096,11 @@
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2906,8 +3128,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2935,8 +3160,11 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -2964,8 +3192,11 @@
       <c r="K94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2977,8 +3208,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3006,8 +3238,11 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3035,8 +3270,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3064,8 +3302,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3093,8 +3334,11 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3122,8 +3366,11 @@
       <c r="K100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3151,8 +3398,11 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3178,6 +3428,9 @@
         <v>5</v>
       </c>
       <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FABP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FABP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
   <si>
     <t>FABP</t>
   </si>
@@ -656,96 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E8" s="3">
         <v>10000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8800</v>
-      </c>
-      <c r="I8" s="3">
-        <v>7600</v>
       </c>
       <c r="J8" s="3">
         <v>7600</v>
       </c>
       <c r="K8" s="3">
+        <v>7600</v>
+      </c>
+      <c r="L8" s="3">
         <v>8400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -776,40 +783,46 @@
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E10" s="3">
         <v>10000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8800</v>
-      </c>
-      <c r="I10" s="3">
-        <v>7600</v>
       </c>
       <c r="J10" s="3">
         <v>7600</v>
       </c>
       <c r="K10" s="3">
+        <v>7600</v>
+      </c>
+      <c r="L10" s="3">
         <v>8400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -822,8 +835,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -854,8 +868,11 @@
       <c r="L12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -886,8 +903,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -918,8 +938,11 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -950,8 +973,11 @@
       <c r="L15" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -961,72 +987,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E17" s="3">
         <v>6600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E18" s="3">
         <v>3400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1039,8 +1072,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1066,45 +1100,51 @@
         <v>100</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E21" s="3">
         <v>3500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>2600</v>
       </c>
       <c r="H21" s="3">
         <v>2600</v>
       </c>
       <c r="I21" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J21" s="3">
         <v>1700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1135,72 +1175,81 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E23" s="3">
         <v>3300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1231,72 +1280,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
-      </c>
-      <c r="G26" s="3">
-        <v>2100</v>
       </c>
       <c r="H26" s="3">
         <v>2100</v>
       </c>
       <c r="I26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J26" s="3">
         <v>1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>2100</v>
       </c>
       <c r="H27" s="3">
         <v>2100</v>
       </c>
       <c r="I27" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J27" s="3">
         <v>1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1327,8 +1385,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1359,8 +1420,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1391,8 +1455,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1423,8 +1490,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1450,45 +1520,51 @@
         <v>-100</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>2100</v>
       </c>
       <c r="H33" s="3">
         <v>2100</v>
       </c>
       <c r="I33" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J33" s="3">
         <v>1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1519,77 +1595,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>2100</v>
       </c>
       <c r="H35" s="3">
         <v>2100</v>
       </c>
       <c r="I35" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J35" s="3">
         <v>1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1602,8 +1687,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1616,40 +1702,44 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E41" s="3">
         <v>23700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>46600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>51200</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J41" s="3">
         <v>68900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>35200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18600</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1660,11 +1750,11 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>800</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -1672,16 +1762,19 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>1300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>700</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1712,8 +1805,11 @@
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1744,136 +1840,151 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E45" s="3">
         <v>19700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>18000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>19000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>25200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>22200</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E46" s="3">
         <v>43900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>41200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>69500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>70900</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" s="3">
         <v>96600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>59800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>41800</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>190600</v>
+      </c>
+      <c r="E47" s="3">
         <v>187000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>192800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>177400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>186100</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3">
         <v>173300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>181400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>188300</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E48" s="3">
         <v>18700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13500</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>10900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8100</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1904,8 +2015,11 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1936,8 +2050,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1968,40 +2085,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E52" s="3">
         <v>26500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>23800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>23700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>23600</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="3">
         <v>23400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>23300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>23200</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2032,40 +2155,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1048300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1038300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>995700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>987700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>992200</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J54" s="3">
         <v>948800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>898500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>851700</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2078,8 +2207,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2092,72 +2222,79 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>810000</v>
+      </c>
+      <c r="E57" s="3">
         <v>743200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>774900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>759000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>731200</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3">
         <v>700300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>664900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>640800</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E58" s="3">
         <v>43200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>44900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>94100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>69000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>67700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>66300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>31800</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2188,80 +2325,89 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>862000</v>
+      </c>
+      <c r="E60" s="3">
         <v>795000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>828500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>865200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>811100</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="3">
         <v>777000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>741200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>679100</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>112300</v>
+      </c>
+      <c r="E61" s="3">
         <v>172300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>92400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>54700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>112000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>112100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>91100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>109700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>5</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>5</v>
@@ -2284,8 +2430,11 @@
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2316,8 +2465,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2348,8 +2500,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2380,40 +2535,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>974300</v>
+      </c>
+      <c r="E66" s="3">
         <v>967300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>920900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>919900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>923100</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J66" s="3">
         <v>889200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>832400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>788800</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2426,8 +2587,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2458,8 +2620,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2490,8 +2655,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2522,8 +2690,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2554,40 +2725,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E72" s="3">
         <v>90700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>88600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>87200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>88800</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3">
         <v>85900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>86700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>83400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2618,8 +2795,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2650,8 +2830,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2682,40 +2865,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E76" s="3">
         <v>71000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>74800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>67800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>69100</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="I76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J76" s="3">
         <v>59700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>66100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>62900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>60700</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2746,77 +2935,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>2100</v>
       </c>
       <c r="H81" s="3">
         <v>2100</v>
       </c>
       <c r="I81" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J81" s="3">
         <v>1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2829,8 +3027,9 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2861,8 +3060,11 @@
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2893,8 +3095,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2925,8 +3130,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2957,8 +3165,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2989,8 +3200,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3021,8 +3235,11 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3053,8 +3270,11 @@
       <c r="L89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3067,8 +3287,9 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3099,8 +3320,11 @@
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3131,8 +3355,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3163,8 +3390,11 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3195,8 +3425,11 @@
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3209,8 +3442,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3241,8 +3475,11 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3273,8 +3510,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3305,8 +3545,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3337,8 +3580,11 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3369,8 +3615,11 @@
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3401,8 +3650,11 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3431,6 +3683,9 @@
         <v>5</v>
       </c>
       <c r="L102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FABP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FABP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="92">
   <si>
     <t>FABP</t>
   </si>
@@ -656,103 +656,110 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>9600</v>
-      </c>
-      <c r="E8" s="3">
-        <v>10000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>8800</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3">
         <v>4900</v>
       </c>
-      <c r="H8" s="3">
-        <v>9100</v>
-      </c>
-      <c r="I8" s="3">
-        <v>8800</v>
-      </c>
-      <c r="J8" s="3">
-        <v>7600</v>
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K8" s="3">
         <v>7600</v>
       </c>
       <c r="L8" s="3">
+        <v>7600</v>
+      </c>
+      <c r="M8" s="3">
         <v>8400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -786,43 +793,49 @@
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>9600</v>
-      </c>
-      <c r="E10" s="3">
-        <v>10000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>8800</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3">
         <v>4900</v>
       </c>
-      <c r="H10" s="3">
-        <v>9100</v>
-      </c>
-      <c r="I10" s="3">
-        <v>8800</v>
-      </c>
-      <c r="J10" s="3">
-        <v>7600</v>
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K10" s="3">
         <v>7600</v>
       </c>
       <c r="L10" s="3">
+        <v>7600</v>
+      </c>
+      <c r="M10" s="3">
         <v>8400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,8 +849,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -871,8 +885,11 @@
       <c r="M12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,8 +923,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -941,31 +961,34 @@
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>200</v>
@@ -976,8 +999,11 @@
       <c r="M15" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,78 +1014,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>7100</v>
-      </c>
-      <c r="E17" s="3">
-        <v>6600</v>
-      </c>
-      <c r="F17" s="3">
-        <v>6300</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3">
         <v>6400</v>
       </c>
-      <c r="H17" s="3">
-        <v>6500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>6300</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3">
         <v>5900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>2500</v>
-      </c>
-      <c r="E18" s="3">
-        <v>3400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3">
         <v>-1500</v>
       </c>
-      <c r="H18" s="3">
-        <v>2600</v>
-      </c>
-      <c r="I18" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3">
         <v>1700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1073,78 +1106,85 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L21" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M21" s="3">
         <v>3500</v>
       </c>
-      <c r="F21" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="H21" s="3">
-        <v>2600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J21" s="3">
-        <v>1700</v>
-      </c>
-      <c r="K21" s="3">
-        <v>2200</v>
-      </c>
-      <c r="L21" s="3">
-        <v>3500</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1178,78 +1218,87 @@
       <c r="M22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>2400</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M23" s="3">
         <v>3300</v>
       </c>
-      <c r="F23" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="H23" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I23" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J23" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K23" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L23" s="3">
-        <v>3300</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
+        <v>100</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="M24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
-        <v>300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-600</v>
-      </c>
-      <c r="H24" s="3">
-        <v>400</v>
-      </c>
-      <c r="I24" s="3">
-        <v>300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>100</v>
-      </c>
-      <c r="K24" s="3">
-        <v>300</v>
-      </c>
-      <c r="L24" s="3">
-        <v>500</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,78 +1332,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>2000</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M26" s="3">
         <v>2800</v>
       </c>
-      <c r="F26" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-900</v>
-      </c>
-      <c r="H26" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K26" s="3">
-        <v>1700</v>
-      </c>
-      <c r="L26" s="3">
-        <v>2800</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>2000</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M27" s="3">
         <v>2800</v>
       </c>
-      <c r="F27" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="H27" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K27" s="3">
-        <v>1700</v>
-      </c>
-      <c r="L27" s="3">
-        <v>2800</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,8 +1446,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,8 +1484,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1522,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,78 +1560,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>2000</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M33" s="3">
         <v>2800</v>
       </c>
-      <c r="F33" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="H33" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K33" s="3">
-        <v>1700</v>
-      </c>
-      <c r="L33" s="3">
-        <v>2800</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,83 +1674,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>2000</v>
-      </c>
-      <c r="E35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M35" s="3">
         <v>2800</v>
       </c>
-      <c r="F35" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="H35" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J35" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K35" s="3">
-        <v>1700</v>
-      </c>
-      <c r="L35" s="3">
-        <v>2800</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +1773,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,43 +1789,47 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>30200</v>
-      </c>
-      <c r="E41" s="3">
-        <v>23700</v>
-      </c>
-      <c r="F41" s="3">
-        <v>22000</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" s="3">
         <v>46600</v>
       </c>
-      <c r="H41" s="3">
-        <v>51200</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K41" s="3">
         <v>68900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>35200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18600</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1753,11 +1843,11 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>800</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -1765,16 +1855,19 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>1300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>700</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1808,8 +1901,11 @@
       <c r="M43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1843,171 +1939,186 @@
       <c r="M44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>19100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>19700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>18000</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>21300</v>
       </c>
-      <c r="H45" s="3">
-        <v>19000</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
         <v>25200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>22800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>22200</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>49300</v>
-      </c>
-      <c r="E46" s="3">
-        <v>43900</v>
-      </c>
-      <c r="F46" s="3">
-        <v>41200</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H46" s="3">
         <v>69500</v>
       </c>
-      <c r="H46" s="3">
-        <v>70900</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K46" s="3">
         <v>96600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>59800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>41800</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>190600</v>
-      </c>
-      <c r="E47" s="3">
-        <v>187000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>192800</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3">
         <v>177400</v>
       </c>
-      <c r="H47" s="3">
-        <v>186100</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K47" s="3">
         <v>173300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>181400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>188300</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>19400</v>
-      </c>
-      <c r="E48" s="3">
-        <v>18700</v>
-      </c>
-      <c r="F48" s="3">
-        <v>17300</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3">
         <v>13700</v>
       </c>
-      <c r="H48" s="3">
-        <v>13500</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K48" s="3">
         <v>10900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8100</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
+      <c r="D49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="I49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -2018,8 +2129,11 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2167,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,43 +2205,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>26600</v>
-      </c>
-      <c r="E52" s="3">
-        <v>26500</v>
-      </c>
-      <c r="F52" s="3">
-        <v>23800</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3">
         <v>23700</v>
       </c>
-      <c r="H52" s="3">
-        <v>23600</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3">
         <v>23400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>23300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>23200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,43 +2281,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>1048300</v>
-      </c>
-      <c r="E54" s="3">
-        <v>1038300</v>
-      </c>
-      <c r="F54" s="3">
-        <v>995700</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H54" s="3">
         <v>987700</v>
       </c>
-      <c r="H54" s="3">
-        <v>992200</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K54" s="3">
         <v>948800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>898500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>851700</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2337,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,78 +2353,85 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>810000</v>
-      </c>
-      <c r="E57" s="3">
-        <v>743200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>774900</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3">
         <v>759000</v>
       </c>
-      <c r="H57" s="3">
-        <v>731200</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K57" s="3">
         <v>700300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>664900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>640800</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>43600</v>
-      </c>
-      <c r="E58" s="3">
-        <v>43200</v>
-      </c>
-      <c r="F58" s="3">
-        <v>44900</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="3">
         <v>94100</v>
       </c>
-      <c r="H58" s="3">
-        <v>69000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="I58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K58" s="3">
         <v>67700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>66300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>31800</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2328,86 +2465,95 @@
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>862000</v>
-      </c>
-      <c r="E60" s="3">
-        <v>795000</v>
-      </c>
-      <c r="F60" s="3">
-        <v>828500</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="3">
         <v>865200</v>
       </c>
-      <c r="H60" s="3">
-        <v>811100</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K60" s="3">
         <v>777000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>741200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>679100</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>112300</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>172300</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>92400</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>54700</v>
       </c>
-      <c r="H61" s="3">
-        <v>112000</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>112100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>91100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>109700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>5</v>
@@ -2433,8 +2579,11 @@
       <c r="M62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +2617,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +2655,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,43 +2693,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>974300</v>
-      </c>
-      <c r="E66" s="3">
-        <v>967300</v>
-      </c>
-      <c r="F66" s="3">
-        <v>920900</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H66" s="3">
         <v>919900</v>
       </c>
-      <c r="H66" s="3">
-        <v>923100</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K66" s="3">
         <v>889200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>832400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>788800</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +2749,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +2785,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +2823,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2693,8 +2861,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,43 +2899,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>92000</v>
-      </c>
-      <c r="E72" s="3">
-        <v>90700</v>
-      </c>
-      <c r="F72" s="3">
-        <v>88600</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="3">
         <v>87200</v>
       </c>
-      <c r="H72" s="3">
-        <v>88800</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K72" s="3">
         <v>85900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>86700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>83400</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +2975,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3013,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,43 +3051,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>74000</v>
-      </c>
-      <c r="E76" s="3">
-        <v>71000</v>
-      </c>
-      <c r="F76" s="3">
-        <v>74800</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H76" s="3">
         <v>67800</v>
       </c>
-      <c r="H76" s="3">
-        <v>69100</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K76" s="3">
         <v>59700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>66100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>62900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>60700</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,83 +3127,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>2000</v>
-      </c>
-      <c r="E81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M81" s="3">
         <v>2800</v>
       </c>
-      <c r="F81" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="H81" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J81" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K81" s="3">
-        <v>1700</v>
-      </c>
-      <c r="L81" s="3">
-        <v>2800</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,8 +3226,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3063,8 +3262,11 @@
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +3300,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +3338,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +3376,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +3414,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,8 +3452,11 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3273,8 +3490,11 @@
       <c r="M89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,8 +3508,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3323,8 +3544,11 @@
       <c r="M91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +3582,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,8 +3620,11 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3428,8 +3658,11 @@
       <c r="M94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,8 +3676,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3478,8 +3712,11 @@
       <c r="M96" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +3750,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +3788,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,8 +3826,11 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3618,8 +3864,11 @@
       <c r="M100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3653,8 +3902,11 @@
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3686,6 +3938,9 @@
         <v>5</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FABP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FABP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>FABP</t>
   </si>
@@ -656,107 +656,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
-        <v>35885</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>35795</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E8" s="3">
         <v>10000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
+        <v>10000</v>
+      </c>
+      <c r="G8" s="3">
         <v>4900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>7600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>7900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>7700</v>
       </c>
-      <c r="I8" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3400</v>
-      </c>
-      <c r="K8" s="3">
-        <v>7600</v>
       </c>
       <c r="L8" s="3">
         <v>7600</v>
       </c>
       <c r="M8" s="3">
+        <v>7600</v>
+      </c>
+      <c r="N8" s="3">
         <v>8400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -793,46 +801,52 @@
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E10" s="3">
         <v>10000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
+        <v>10000</v>
+      </c>
+      <c r="G10" s="3">
         <v>4900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>7600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>7900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>7700</v>
       </c>
-      <c r="I10" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3400</v>
-      </c>
-      <c r="K10" s="3">
-        <v>7600</v>
       </c>
       <c r="L10" s="3">
         <v>7600</v>
       </c>
       <c r="M10" s="3">
+        <v>7600</v>
+      </c>
+      <c r="N10" s="3">
         <v>8400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -847,8 +861,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -885,8 +900,11 @@
       <c r="N12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -923,8 +941,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -940,15 +961,15 @@
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>-700</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
@@ -961,13 +982,16 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
@@ -982,13 +1006,13 @@
         <v>200</v>
       </c>
       <c r="I15" s="3">
+        <v>200</v>
+      </c>
+      <c r="J15" s="3">
+        <v>200</v>
+      </c>
+      <c r="K15" s="3">
         <v>100</v>
-      </c>
-      <c r="J15" s="3">
-        <v>100</v>
-      </c>
-      <c r="K15" s="3">
-        <v>200</v>
       </c>
       <c r="L15" s="3">
         <v>200</v>
@@ -999,8 +1023,11 @@
       <c r="N15" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1012,84 +1039,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E17" s="3">
         <v>7000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
+        <v>6600</v>
+      </c>
+      <c r="G17" s="3">
         <v>6400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1900</v>
       </c>
-      <c r="J17" s="3">
-        <v>1900</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E18" s="3">
         <v>2900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G18" s="3">
         <v>-1500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>2100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>3000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2500</v>
       </c>
-      <c r="I18" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1104,8 +1138,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1122,66 +1157,72 @@
         <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K20" s="3">
         <v>100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E21" s="3">
         <v>3100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>2200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>3100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>2600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J21" s="3">
-        <v>1700</v>
       </c>
       <c r="K21" s="3">
         <v>1700</v>
       </c>
       <c r="L21" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M21" s="3">
         <v>2200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1218,84 +1259,93 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G23" s="3">
         <v>-1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>2900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>3200</v>
       </c>
-      <c r="I23" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
+        <v>500</v>
+      </c>
+      <c r="G24" s="3">
         <v>-600</v>
-      </c>
-      <c r="F24" s="3">
-        <v>300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>400</v>
       </c>
       <c r="H24" s="3">
         <v>300</v>
       </c>
       <c r="I24" s="3">
+        <v>400</v>
+      </c>
+      <c r="J24" s="3">
+        <v>300</v>
+      </c>
+      <c r="K24" s="3">
+        <v>600</v>
+      </c>
+      <c r="L24" s="3">
+        <v>100</v>
+      </c>
+      <c r="M24" s="3">
+        <v>300</v>
+      </c>
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="O24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
-        <v>100</v>
-      </c>
-      <c r="L24" s="3">
-        <v>300</v>
-      </c>
-      <c r="M24" s="3">
-        <v>500</v>
-      </c>
-      <c r="N24" s="3">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1332,84 +1382,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E26" s="3">
         <v>2400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>2500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>2900</v>
       </c>
-      <c r="I26" s="3">
-        <v>900</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E27" s="3">
         <v>2400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>2500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>2900</v>
       </c>
-      <c r="I27" s="3">
-        <v>900</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1446,8 +1505,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1484,8 +1546,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1522,8 +1587,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1560,8 +1628,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1578,66 +1649,72 @@
         <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K32" s="3">
         <v>-100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E33" s="3">
         <v>2400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>2500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>2900</v>
       </c>
-      <c r="I33" s="3">
-        <v>900</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1674,89 +1751,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E35" s="3">
         <v>2400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>2500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>2900</v>
       </c>
-      <c r="I35" s="3">
-        <v>900</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
-        <v>35885</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>35795</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1771,8 +1857,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1787,84 +1874,91 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E41" s="3">
         <v>66200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
+        <v>23700</v>
+      </c>
+      <c r="G41" s="3">
         <v>46600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>35200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>20500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>59800</v>
       </c>
-      <c r="I41" s="3">
-        <v>12700</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>68900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>35200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>18600</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>800</v>
+      </c>
+      <c r="E42" s="3">
         <v>500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>1300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>1900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1400</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>1300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>700</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1901,8 +1995,11 @@
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1939,160 +2036,175 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E45" s="3">
         <v>22000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
+        <v>19700</v>
+      </c>
+      <c r="G45" s="3">
         <v>21300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>22800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>18900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>12800</v>
       </c>
-      <c r="I45" s="3">
-        <v>9100</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>25200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>22800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>22200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>95500</v>
+      </c>
+      <c r="E46" s="3">
         <v>88700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
+        <v>43900</v>
+      </c>
+      <c r="G46" s="3">
         <v>69500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>59800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>42100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>74600</v>
       </c>
-      <c r="I46" s="3">
-        <v>23500</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>96600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>59800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>41800</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>202800</v>
+      </c>
+      <c r="E47" s="3">
         <v>190100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
+        <v>194200</v>
+      </c>
+      <c r="G47" s="3">
         <v>177400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>181400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>200600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>198800</v>
       </c>
-      <c r="I47" s="3">
-        <v>29600</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>30500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>173300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>181400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>188300</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E48" s="3">
         <v>16900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
+        <v>18700</v>
+      </c>
+      <c r="G48" s="3">
         <v>13700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>8500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>8200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>7100</v>
       </c>
-      <c r="I48" s="3">
-        <v>5300</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8100</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2129,8 +2241,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2167,8 +2282,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2205,46 +2323,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E52" s="3">
         <v>26700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
+        <v>19400</v>
+      </c>
+      <c r="G52" s="3">
         <v>23700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>23300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>20100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>19900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1300</v>
       </c>
-      <c r="J52" s="3">
-        <v>1300</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>23400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>23300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2281,46 +2405,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1142000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1102500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
+        <v>1038300</v>
+      </c>
+      <c r="G54" s="3">
         <v>987700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>898500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>789400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>761800</v>
       </c>
-      <c r="I54" s="3">
-        <v>265100</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>266700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>948800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>898500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>851700</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2335,8 +2465,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2351,84 +2482,91 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>919600</v>
+      </c>
+      <c r="E57" s="3">
         <v>851300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
+        <v>743200</v>
+      </c>
+      <c r="G57" s="3">
         <v>759000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>664900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>668300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>627200</v>
       </c>
-      <c r="I57" s="3">
-        <v>213600</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>216800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>700300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>664900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>640800</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E58" s="3">
         <v>54300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
+        <v>43200</v>
+      </c>
+      <c r="G58" s="3">
         <v>45600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>66300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>25200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>32100</v>
       </c>
-      <c r="I58" s="3">
-        <v>10500</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>67700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>66300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>31800</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2465,84 +2603,93 @@
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>937500</v>
+      </c>
+      <c r="E60" s="3">
         <v>916900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
+        <v>795000</v>
+      </c>
+      <c r="G60" s="3">
         <v>816700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>741200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>701400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>665200</v>
       </c>
-      <c r="I60" s="3">
-        <v>227000</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>229000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>777000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>741200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>679100</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>119800</v>
+      </c>
+      <c r="E61" s="3">
         <v>109800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
+        <v>172300</v>
+      </c>
+      <c r="G61" s="3">
         <v>103200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>91100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>27400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>7700</v>
       </c>
-      <c r="I61" s="3">
-        <v>10700</v>
-      </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>112100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>91100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>109700</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2552,8 +2699,8 @@
       <c r="E62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>5</v>
+      <c r="F62" s="3">
+        <v>0</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>5</v>
@@ -2579,8 +2726,11 @@
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2617,8 +2767,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2655,8 +2808,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2693,46 +2849,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1057200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1026700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
+        <v>967300</v>
+      </c>
+      <c r="G66" s="3">
         <v>919900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>832400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>728800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>672800</v>
       </c>
-      <c r="I66" s="3">
-        <v>237700</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>239900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>889200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>832400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>788800</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2747,8 +2909,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2785,8 +2948,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2823,8 +2989,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2861,8 +3030,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2899,46 +3071,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>97500</v>
+      </c>
+      <c r="E72" s="3">
         <v>93700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
+        <v>90700</v>
+      </c>
+      <c r="G72" s="3">
         <v>87200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>86700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>78800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>82600</v>
       </c>
-      <c r="I72" s="3">
-        <v>19400</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>85900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>86700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>83400</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2975,8 +3153,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3013,8 +3194,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3051,46 +3235,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>84700</v>
+      </c>
+      <c r="E76" s="3">
         <v>75800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
+        <v>71000</v>
+      </c>
+      <c r="G76" s="3">
         <v>67800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>66100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>60700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>89000</v>
       </c>
-      <c r="I76" s="3">
-        <v>27400</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>26800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>59700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>66100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>62900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>60700</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3127,89 +3317,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
-        <v>35885</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>35795</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E81" s="3">
         <v>2400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>2500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>2900</v>
       </c>
-      <c r="I81" s="3">
-        <v>900</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3224,8 +3423,9 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3241,15 +3441,15 @@
       <c r="G83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3">
         <v>600</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
@@ -3262,8 +3462,11 @@
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3300,8 +3503,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3338,8 +3544,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3376,8 +3585,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3414,8 +3626,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3452,8 +3667,11 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3472,15 +3690,15 @@
       <c r="H89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I89" s="3">
-        <v>200</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
         <v>600</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>5</v>
       </c>
@@ -3490,8 +3708,11 @@
       <c r="N89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3506,8 +3727,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3526,15 +3748,15 @@
       <c r="H91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
@@ -3544,8 +3766,11 @@
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3582,8 +3807,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3620,8 +3848,11 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3640,15 +3871,15 @@
       <c r="H94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I94" s="3">
-        <v>5500</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
         <v>-3800</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
@@ -3658,8 +3889,11 @@
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3674,8 +3908,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3712,8 +3947,11 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3750,8 +3988,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3788,8 +4029,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3826,8 +4070,11 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3846,15 +4093,15 @@
       <c r="H100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I100" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
         <v>3000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
@@ -3864,8 +4111,11 @@
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3902,8 +4152,11 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3923,14 +4176,14 @@
         <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>5</v>
       </c>
@@ -3938,6 +4191,9 @@
         <v>5</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
